--- a/project/99_presentation_project/L03_rv32i_single_cycle_cpu/my_cpu.xlsx
+++ b/project/99_presentation_project/L03_rv32i_single_cycle_cpu/my_cpu.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\project_2026\Verilog_2026_Project\project\99_presentation_project\L03_rv32i_single_cycle_cpu\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\class_verilog\Verilog_2026_Project\project\99_presentation_project\L03_rv32i_single_cycle_cpu\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3194102-1731-4C82-8C2A-E10CC9859E88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25490" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="25485" yWindow="-105" windowWidth="19425" windowHeight="10305"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="94">
   <si>
     <t>funct7</t>
   </si>
@@ -340,10 +339,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>a &lt;= b</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>S</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -377,13 +372,21 @@
   </si>
   <si>
     <t>(a&lt;b)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>a &gt;= b</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>a &gt;= b</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -901,114 +904,6 @@
     <xf numFmtId="0" fontId="0" fillId="14" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="4" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="5" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="6" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="4" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="5" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="6" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="4" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="5" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="6" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="4" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="5" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="6" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
@@ -1019,10 +914,118 @@
     <xf numFmtId="0" fontId="5" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="4" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="5" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="6" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="4" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="5" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="6" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="4" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="5" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="6" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="4" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="5" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="6" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
-    <cellStyle name="표준 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
+    <cellStyle name="표준 2" xfId="1"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1299,14 +1302,14 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:AG48"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="4" max="5" width="9" customWidth="1"/>
-    <col min="6" max="6" width="9" style="58" customWidth="1"/>
-    <col min="7" max="8" width="9" customWidth="1"/>
-    <col min="10" max="14" width="9" customWidth="1"/>
+    <col min="2" max="5" width="9" customWidth="1"/>
+    <col min="6" max="6" width="9" style="22" customWidth="1"/>
+    <col min="7" max="14" width="9" customWidth="1"/>
+    <col min="18" max="18" width="9" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:33" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -1317,7 +1320,7 @@
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
-      <c r="F1" s="57"/>
+      <c r="F1" s="21"/>
       <c r="G1" s="2">
         <v>25</v>
       </c>
@@ -1368,281 +1371,281 @@
       </c>
     </row>
     <row r="2" spans="1:33" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="50" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="51"/>
-      <c r="C2" s="51"/>
-      <c r="D2" s="51"/>
-      <c r="E2" s="51"/>
-      <c r="F2" s="51"/>
-      <c r="G2" s="52"/>
-      <c r="H2" s="44" t="s">
+      <c r="A2" s="44" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="45"/>
+      <c r="C2" s="45"/>
+      <c r="D2" s="45"/>
+      <c r="E2" s="45"/>
+      <c r="F2" s="45"/>
+      <c r="G2" s="46"/>
+      <c r="H2" s="36" t="s">
         <v>1</v>
       </c>
-      <c r="I2" s="45"/>
-      <c r="J2" s="45"/>
-      <c r="K2" s="45"/>
-      <c r="L2" s="46"/>
-      <c r="M2" s="47" t="s">
+      <c r="I2" s="37"/>
+      <c r="J2" s="37"/>
+      <c r="K2" s="37"/>
+      <c r="L2" s="38"/>
+      <c r="M2" s="33" t="s">
         <v>2</v>
       </c>
-      <c r="N2" s="48"/>
-      <c r="O2" s="48"/>
-      <c r="P2" s="48"/>
-      <c r="Q2" s="49"/>
-      <c r="R2" s="50" t="s">
+      <c r="N2" s="34"/>
+      <c r="O2" s="34"/>
+      <c r="P2" s="34"/>
+      <c r="Q2" s="35"/>
+      <c r="R2" s="44" t="s">
         <v>3</v>
       </c>
-      <c r="S2" s="51"/>
-      <c r="T2" s="52"/>
-      <c r="U2" s="47" t="s">
+      <c r="S2" s="45"/>
+      <c r="T2" s="46"/>
+      <c r="U2" s="33" t="s">
         <v>4</v>
       </c>
-      <c r="V2" s="48"/>
-      <c r="W2" s="48"/>
-      <c r="X2" s="48"/>
-      <c r="Y2" s="49"/>
-      <c r="Z2" s="44" t="s">
+      <c r="V2" s="34"/>
+      <c r="W2" s="34"/>
+      <c r="X2" s="34"/>
+      <c r="Y2" s="35"/>
+      <c r="Z2" s="36" t="s">
         <v>5</v>
       </c>
-      <c r="AA2" s="45"/>
-      <c r="AB2" s="45"/>
-      <c r="AC2" s="45"/>
-      <c r="AD2" s="45"/>
-      <c r="AE2" s="45"/>
-      <c r="AF2" s="46"/>
+      <c r="AA2" s="37"/>
+      <c r="AB2" s="37"/>
+      <c r="AC2" s="37"/>
+      <c r="AD2" s="37"/>
+      <c r="AE2" s="37"/>
+      <c r="AF2" s="38"/>
       <c r="AG2" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:33" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="41" t="s">
+      <c r="A3" s="30" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="42"/>
-      <c r="C3" s="42"/>
-      <c r="D3" s="42"/>
-      <c r="E3" s="42"/>
-      <c r="F3" s="42"/>
-      <c r="G3" s="43"/>
-      <c r="H3" s="44" t="s">
+      <c r="B3" s="31"/>
+      <c r="C3" s="31"/>
+      <c r="D3" s="31"/>
+      <c r="E3" s="31"/>
+      <c r="F3" s="31"/>
+      <c r="G3" s="32"/>
+      <c r="H3" s="36" t="s">
         <v>1</v>
       </c>
-      <c r="I3" s="45"/>
-      <c r="J3" s="45"/>
-      <c r="K3" s="45"/>
-      <c r="L3" s="46"/>
-      <c r="M3" s="47" t="s">
+      <c r="I3" s="37"/>
+      <c r="J3" s="37"/>
+      <c r="K3" s="37"/>
+      <c r="L3" s="38"/>
+      <c r="M3" s="33" t="s">
         <v>2</v>
       </c>
-      <c r="N3" s="48"/>
-      <c r="O3" s="48"/>
-      <c r="P3" s="48"/>
-      <c r="Q3" s="49"/>
-      <c r="R3" s="50" t="s">
+      <c r="N3" s="34"/>
+      <c r="O3" s="34"/>
+      <c r="P3" s="34"/>
+      <c r="Q3" s="35"/>
+      <c r="R3" s="44" t="s">
         <v>3</v>
       </c>
-      <c r="S3" s="51"/>
-      <c r="T3" s="52"/>
-      <c r="U3" s="41" t="s">
+      <c r="S3" s="45"/>
+      <c r="T3" s="46"/>
+      <c r="U3" s="30" t="s">
         <v>8</v>
       </c>
-      <c r="V3" s="42"/>
-      <c r="W3" s="42"/>
-      <c r="X3" s="42"/>
-      <c r="Y3" s="43"/>
-      <c r="Z3" s="44" t="s">
+      <c r="V3" s="31"/>
+      <c r="W3" s="31"/>
+      <c r="X3" s="31"/>
+      <c r="Y3" s="32"/>
+      <c r="Z3" s="36" t="s">
         <v>5</v>
       </c>
-      <c r="AA3" s="45"/>
-      <c r="AB3" s="45"/>
-      <c r="AC3" s="45"/>
-      <c r="AD3" s="45"/>
-      <c r="AE3" s="45"/>
-      <c r="AF3" s="46"/>
+      <c r="AA3" s="37"/>
+      <c r="AB3" s="37"/>
+      <c r="AC3" s="37"/>
+      <c r="AD3" s="37"/>
+      <c r="AE3" s="37"/>
+      <c r="AF3" s="38"/>
       <c r="AG3" s="1" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:33" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="41" t="s">
+      <c r="A4" s="30" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="42"/>
-      <c r="C4" s="42"/>
-      <c r="D4" s="42"/>
-      <c r="E4" s="42"/>
-      <c r="F4" s="42"/>
-      <c r="G4" s="43"/>
-      <c r="H4" s="44" t="s">
+      <c r="B4" s="31"/>
+      <c r="C4" s="31"/>
+      <c r="D4" s="31"/>
+      <c r="E4" s="31"/>
+      <c r="F4" s="31"/>
+      <c r="G4" s="32"/>
+      <c r="H4" s="36" t="s">
         <v>1</v>
       </c>
-      <c r="I4" s="45"/>
-      <c r="J4" s="45"/>
-      <c r="K4" s="45"/>
-      <c r="L4" s="46"/>
-      <c r="M4" s="47" t="s">
+      <c r="I4" s="37"/>
+      <c r="J4" s="37"/>
+      <c r="K4" s="37"/>
+      <c r="L4" s="38"/>
+      <c r="M4" s="33" t="s">
         <v>2</v>
       </c>
-      <c r="N4" s="48"/>
-      <c r="O4" s="48"/>
-      <c r="P4" s="48"/>
-      <c r="Q4" s="49"/>
-      <c r="R4" s="50" t="s">
+      <c r="N4" s="34"/>
+      <c r="O4" s="34"/>
+      <c r="P4" s="34"/>
+      <c r="Q4" s="35"/>
+      <c r="R4" s="44" t="s">
         <v>3</v>
       </c>
-      <c r="S4" s="51"/>
-      <c r="T4" s="52"/>
-      <c r="U4" s="41" t="s">
+      <c r="S4" s="45"/>
+      <c r="T4" s="46"/>
+      <c r="U4" s="30" t="s">
         <v>11</v>
       </c>
-      <c r="V4" s="42"/>
-      <c r="W4" s="42"/>
-      <c r="X4" s="42"/>
-      <c r="Y4" s="43"/>
-      <c r="Z4" s="44" t="s">
+      <c r="V4" s="31"/>
+      <c r="W4" s="31"/>
+      <c r="X4" s="31"/>
+      <c r="Y4" s="32"/>
+      <c r="Z4" s="36" t="s">
         <v>5</v>
       </c>
-      <c r="AA4" s="45"/>
-      <c r="AB4" s="45"/>
-      <c r="AC4" s="45"/>
-      <c r="AD4" s="45"/>
-      <c r="AE4" s="45"/>
-      <c r="AF4" s="46"/>
+      <c r="AA4" s="37"/>
+      <c r="AB4" s="37"/>
+      <c r="AC4" s="37"/>
+      <c r="AD4" s="37"/>
+      <c r="AE4" s="37"/>
+      <c r="AF4" s="38"/>
       <c r="AG4" s="1" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:33" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="41" t="s">
+      <c r="A5" s="30" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="42"/>
-      <c r="C5" s="42"/>
-      <c r="D5" s="42"/>
-      <c r="E5" s="42"/>
-      <c r="F5" s="42"/>
-      <c r="G5" s="42"/>
-      <c r="H5" s="42"/>
-      <c r="I5" s="42"/>
-      <c r="J5" s="42"/>
-      <c r="K5" s="42"/>
-      <c r="L5" s="43"/>
-      <c r="M5" s="47" t="s">
+      <c r="B5" s="31"/>
+      <c r="C5" s="31"/>
+      <c r="D5" s="31"/>
+      <c r="E5" s="31"/>
+      <c r="F5" s="31"/>
+      <c r="G5" s="31"/>
+      <c r="H5" s="31"/>
+      <c r="I5" s="31"/>
+      <c r="J5" s="31"/>
+      <c r="K5" s="31"/>
+      <c r="L5" s="32"/>
+      <c r="M5" s="33" t="s">
         <v>2</v>
       </c>
-      <c r="N5" s="48"/>
-      <c r="O5" s="48"/>
-      <c r="P5" s="48"/>
-      <c r="Q5" s="49"/>
-      <c r="R5" s="50" t="s">
+      <c r="N5" s="34"/>
+      <c r="O5" s="34"/>
+      <c r="P5" s="34"/>
+      <c r="Q5" s="35"/>
+      <c r="R5" s="44" t="s">
         <v>3</v>
       </c>
-      <c r="S5" s="51"/>
-      <c r="T5" s="52"/>
-      <c r="U5" s="47" t="s">
+      <c r="S5" s="45"/>
+      <c r="T5" s="46"/>
+      <c r="U5" s="33" t="s">
         <v>4</v>
       </c>
-      <c r="V5" s="48"/>
-      <c r="W5" s="48"/>
-      <c r="X5" s="48"/>
-      <c r="Y5" s="49"/>
-      <c r="Z5" s="44" t="s">
+      <c r="V5" s="34"/>
+      <c r="W5" s="34"/>
+      <c r="X5" s="34"/>
+      <c r="Y5" s="35"/>
+      <c r="Z5" s="36" t="s">
         <v>5</v>
       </c>
-      <c r="AA5" s="45"/>
-      <c r="AB5" s="45"/>
-      <c r="AC5" s="45"/>
-      <c r="AD5" s="45"/>
-      <c r="AE5" s="45"/>
-      <c r="AF5" s="46"/>
+      <c r="AA5" s="37"/>
+      <c r="AB5" s="37"/>
+      <c r="AC5" s="37"/>
+      <c r="AD5" s="37"/>
+      <c r="AE5" s="37"/>
+      <c r="AF5" s="38"/>
       <c r="AG5" s="1" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:33" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="41" t="s">
+      <c r="A6" s="30" t="s">
         <v>15</v>
       </c>
-      <c r="B6" s="42"/>
-      <c r="C6" s="42"/>
-      <c r="D6" s="42"/>
-      <c r="E6" s="42"/>
-      <c r="F6" s="42"/>
-      <c r="G6" s="42"/>
-      <c r="H6" s="42"/>
-      <c r="I6" s="42"/>
-      <c r="J6" s="42"/>
-      <c r="K6" s="42"/>
-      <c r="L6" s="42"/>
-      <c r="M6" s="42"/>
-      <c r="N6" s="42"/>
-      <c r="O6" s="42"/>
-      <c r="P6" s="42"/>
-      <c r="Q6" s="42"/>
-      <c r="R6" s="42"/>
-      <c r="S6" s="42"/>
-      <c r="T6" s="43"/>
-      <c r="U6" s="47" t="s">
+      <c r="B6" s="31"/>
+      <c r="C6" s="31"/>
+      <c r="D6" s="31"/>
+      <c r="E6" s="31"/>
+      <c r="F6" s="31"/>
+      <c r="G6" s="31"/>
+      <c r="H6" s="31"/>
+      <c r="I6" s="31"/>
+      <c r="J6" s="31"/>
+      <c r="K6" s="31"/>
+      <c r="L6" s="31"/>
+      <c r="M6" s="31"/>
+      <c r="N6" s="31"/>
+      <c r="O6" s="31"/>
+      <c r="P6" s="31"/>
+      <c r="Q6" s="31"/>
+      <c r="R6" s="31"/>
+      <c r="S6" s="31"/>
+      <c r="T6" s="32"/>
+      <c r="U6" s="33" t="s">
         <v>4</v>
       </c>
-      <c r="V6" s="48"/>
-      <c r="W6" s="48"/>
-      <c r="X6" s="48"/>
-      <c r="Y6" s="49"/>
-      <c r="Z6" s="44" t="s">
+      <c r="V6" s="34"/>
+      <c r="W6" s="34"/>
+      <c r="X6" s="34"/>
+      <c r="Y6" s="35"/>
+      <c r="Z6" s="36" t="s">
         <v>5</v>
       </c>
-      <c r="AA6" s="45"/>
-      <c r="AB6" s="45"/>
-      <c r="AC6" s="45"/>
-      <c r="AD6" s="45"/>
-      <c r="AE6" s="45"/>
-      <c r="AF6" s="46"/>
+      <c r="AA6" s="37"/>
+      <c r="AB6" s="37"/>
+      <c r="AC6" s="37"/>
+      <c r="AD6" s="37"/>
+      <c r="AE6" s="37"/>
+      <c r="AF6" s="38"/>
       <c r="AG6" s="1" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="7" spans="1:33" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="41" t="s">
+      <c r="A7" s="30" t="s">
         <v>17</v>
       </c>
-      <c r="B7" s="42"/>
-      <c r="C7" s="42"/>
-      <c r="D7" s="42"/>
-      <c r="E7" s="42"/>
-      <c r="F7" s="42"/>
-      <c r="G7" s="42"/>
-      <c r="H7" s="42"/>
-      <c r="I7" s="42"/>
-      <c r="J7" s="42"/>
-      <c r="K7" s="42"/>
-      <c r="L7" s="42"/>
-      <c r="M7" s="42"/>
-      <c r="N7" s="42"/>
-      <c r="O7" s="42"/>
-      <c r="P7" s="42"/>
-      <c r="Q7" s="42"/>
-      <c r="R7" s="42"/>
-      <c r="S7" s="42"/>
-      <c r="T7" s="43"/>
-      <c r="U7" s="47" t="s">
+      <c r="B7" s="31"/>
+      <c r="C7" s="31"/>
+      <c r="D7" s="31"/>
+      <c r="E7" s="31"/>
+      <c r="F7" s="31"/>
+      <c r="G7" s="31"/>
+      <c r="H7" s="31"/>
+      <c r="I7" s="31"/>
+      <c r="J7" s="31"/>
+      <c r="K7" s="31"/>
+      <c r="L7" s="31"/>
+      <c r="M7" s="31"/>
+      <c r="N7" s="31"/>
+      <c r="O7" s="31"/>
+      <c r="P7" s="31"/>
+      <c r="Q7" s="31"/>
+      <c r="R7" s="31"/>
+      <c r="S7" s="31"/>
+      <c r="T7" s="32"/>
+      <c r="U7" s="33" t="s">
         <v>4</v>
       </c>
-      <c r="V7" s="48"/>
-      <c r="W7" s="48"/>
-      <c r="X7" s="48"/>
-      <c r="Y7" s="49"/>
-      <c r="Z7" s="44" t="s">
+      <c r="V7" s="34"/>
+      <c r="W7" s="34"/>
+      <c r="X7" s="34"/>
+      <c r="Y7" s="35"/>
+      <c r="Z7" s="36" t="s">
         <v>5</v>
       </c>
-      <c r="AA7" s="45"/>
-      <c r="AB7" s="45"/>
-      <c r="AC7" s="45"/>
-      <c r="AD7" s="45"/>
-      <c r="AE7" s="45"/>
-      <c r="AF7" s="46"/>
+      <c r="AA7" s="37"/>
+      <c r="AB7" s="37"/>
+      <c r="AC7" s="37"/>
+      <c r="AD7" s="37"/>
+      <c r="AE7" s="37"/>
+      <c r="AF7" s="38"/>
       <c r="AG7" s="1" t="s">
         <v>18</v>
       </c>
@@ -1650,37 +1653,37 @@
     <row r="8" spans="1:33" ht="20.25" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="9" spans="1:33" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="10" spans="1:33" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="38" t="s">
+      <c r="A10" s="25" t="s">
         <v>45</v>
       </c>
-      <c r="B10" s="39"/>
-      <c r="C10" s="39"/>
-      <c r="D10" s="39"/>
-      <c r="E10" s="39"/>
-      <c r="F10" s="39"/>
-      <c r="G10" s="39"/>
-      <c r="H10" s="39"/>
-      <c r="I10" s="39"/>
-      <c r="J10" s="39"/>
-      <c r="K10" s="39"/>
-      <c r="L10" s="39"/>
-      <c r="M10" s="39"/>
-      <c r="N10" s="40"/>
+      <c r="B10" s="26"/>
+      <c r="C10" s="26"/>
+      <c r="D10" s="26"/>
+      <c r="E10" s="26"/>
+      <c r="F10" s="26"/>
+      <c r="G10" s="26"/>
+      <c r="H10" s="26"/>
+      <c r="I10" s="26"/>
+      <c r="J10" s="26"/>
+      <c r="K10" s="26"/>
+      <c r="L10" s="26"/>
+      <c r="M10" s="26"/>
+      <c r="N10" s="27"/>
     </row>
     <row r="11" spans="1:33" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="56" t="s">
+      <c r="A11" s="28" t="s">
         <v>44</v>
       </c>
-      <c r="B11" s="21"/>
+      <c r="B11" s="29"/>
       <c r="C11" s="4"/>
-      <c r="D11" s="21" t="s">
+      <c r="D11" s="29" t="s">
         <v>26</v>
       </c>
-      <c r="E11" s="21"/>
-      <c r="F11" s="21" t="s">
+      <c r="E11" s="29"/>
+      <c r="F11" s="29" t="s">
         <v>29</v>
       </c>
-      <c r="G11" s="21"/>
+      <c r="G11" s="29"/>
       <c r="H11" s="4" t="s">
         <v>27</v>
       </c>
@@ -1704,19 +1707,19 @@
       </c>
     </row>
     <row r="12" spans="1:33" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="25" t="s">
+      <c r="A12" s="48" t="s">
         <v>19</v>
       </c>
-      <c r="B12" s="26"/>
+      <c r="B12" s="49"/>
       <c r="C12" s="8"/>
-      <c r="D12" s="22">
+      <c r="D12" s="43">
         <v>1</v>
       </c>
-      <c r="E12" s="22"/>
-      <c r="F12" s="22">
+      <c r="E12" s="43"/>
+      <c r="F12" s="43">
         <v>1</v>
       </c>
-      <c r="G12" s="22"/>
+      <c r="G12" s="43"/>
       <c r="H12" s="3">
         <v>0</v>
       </c>
@@ -1740,19 +1743,19 @@
       </c>
     </row>
     <row r="13" spans="1:33" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="25" t="s">
+      <c r="A13" s="48" t="s">
         <v>20</v>
       </c>
-      <c r="B13" s="26"/>
+      <c r="B13" s="49"/>
       <c r="C13" s="8"/>
-      <c r="D13" s="22">
-        <v>0</v>
-      </c>
-      <c r="E13" s="22"/>
-      <c r="F13" s="22">
+      <c r="D13" s="43">
+        <v>0</v>
+      </c>
+      <c r="E13" s="43"/>
+      <c r="F13" s="43">
         <v>1</v>
       </c>
-      <c r="G13" s="22"/>
+      <c r="G13" s="43"/>
       <c r="H13" s="3">
         <v>1</v>
       </c>
@@ -1776,19 +1779,19 @@
       </c>
     </row>
     <row r="14" spans="1:33" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="25" t="s">
+      <c r="A14" s="48" t="s">
         <v>21</v>
       </c>
-      <c r="B14" s="26"/>
+      <c r="B14" s="49"/>
       <c r="C14" s="8"/>
-      <c r="D14" s="22">
-        <v>0</v>
-      </c>
-      <c r="E14" s="22"/>
-      <c r="F14" s="22">
-        <v>0</v>
-      </c>
-      <c r="G14" s="22"/>
+      <c r="D14" s="43">
+        <v>0</v>
+      </c>
+      <c r="E14" s="43"/>
+      <c r="F14" s="43">
+        <v>0</v>
+      </c>
+      <c r="G14" s="43"/>
       <c r="H14" s="3">
         <v>0</v>
       </c>
@@ -1812,31 +1815,31 @@
       </c>
     </row>
     <row r="15" spans="1:33" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="29" t="s">
+      <c r="A15" s="50" t="s">
         <v>22</v>
       </c>
-      <c r="B15" s="30"/>
+      <c r="B15" s="51"/>
       <c r="C15" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="D15" s="31" t="s">
+      <c r="D15" s="54" t="s">
         <v>38</v>
       </c>
-      <c r="E15" s="32"/>
-      <c r="F15" s="22" t="s">
+      <c r="E15" s="55"/>
+      <c r="F15" s="43" t="s">
         <v>38</v>
       </c>
-      <c r="G15" s="22"/>
-      <c r="H15" s="22" t="s">
+      <c r="G15" s="43"/>
+      <c r="H15" s="43" t="s">
         <v>36</v>
       </c>
-      <c r="I15" s="22" t="s">
+      <c r="I15" s="43" t="s">
         <v>36</v>
       </c>
-      <c r="J15" s="22" t="s">
+      <c r="J15" s="43" t="s">
         <v>42</v>
       </c>
-      <c r="K15" s="22" t="s">
+      <c r="K15" s="43" t="s">
         <v>43</v>
       </c>
       <c r="L15" s="16" t="s">
@@ -1850,23 +1853,23 @@
       </c>
     </row>
     <row r="16" spans="1:33" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="29" t="s">
+      <c r="A16" s="50" t="s">
         <v>46</v>
       </c>
-      <c r="B16" s="30"/>
+      <c r="B16" s="51"/>
       <c r="C16" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="D16" s="33"/>
-      <c r="E16" s="34"/>
-      <c r="F16" s="22" t="s">
+      <c r="D16" s="56"/>
+      <c r="E16" s="57"/>
+      <c r="F16" s="43" t="s">
         <v>39</v>
       </c>
-      <c r="G16" s="22"/>
-      <c r="H16" s="22"/>
-      <c r="I16" s="22"/>
-      <c r="J16" s="22"/>
-      <c r="K16" s="22"/>
+      <c r="G16" s="43"/>
+      <c r="H16" s="43"/>
+      <c r="I16" s="43"/>
+      <c r="J16" s="43"/>
+      <c r="K16" s="43"/>
       <c r="L16" s="17" t="s">
         <v>48</v>
       </c>
@@ -1878,19 +1881,19 @@
       </c>
     </row>
     <row r="17" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="25" t="s">
+      <c r="A17" s="48" t="s">
         <v>37</v>
       </c>
-      <c r="B17" s="26"/>
+      <c r="B17" s="49"/>
       <c r="C17" s="8"/>
-      <c r="D17" s="22">
-        <v>0</v>
-      </c>
-      <c r="E17" s="22"/>
-      <c r="F17" s="22">
-        <v>0</v>
-      </c>
-      <c r="G17" s="22"/>
+      <c r="D17" s="43">
+        <v>0</v>
+      </c>
+      <c r="E17" s="43"/>
+      <c r="F17" s="43">
+        <v>0</v>
+      </c>
+      <c r="G17" s="43"/>
       <c r="H17" s="3">
         <v>0</v>
       </c>
@@ -1914,19 +1917,19 @@
       </c>
     </row>
     <row r="18" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="35" t="s">
+      <c r="A18" s="58" t="s">
         <v>23</v>
       </c>
-      <c r="B18" s="36"/>
+      <c r="B18" s="59"/>
       <c r="C18" s="8"/>
-      <c r="D18" s="22">
-        <v>0</v>
-      </c>
-      <c r="E18" s="22"/>
-      <c r="F18" s="22">
-        <v>0</v>
-      </c>
-      <c r="G18" s="22"/>
+      <c r="D18" s="43">
+        <v>0</v>
+      </c>
+      <c r="E18" s="43"/>
+      <c r="F18" s="43">
+        <v>0</v>
+      </c>
+      <c r="G18" s="43"/>
       <c r="H18" s="3">
         <v>0</v>
       </c>
@@ -1950,19 +1953,19 @@
       </c>
     </row>
     <row r="19" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="25" t="s">
+      <c r="A19" s="48" t="s">
         <v>24</v>
       </c>
-      <c r="B19" s="26"/>
+      <c r="B19" s="49"/>
       <c r="C19" s="8"/>
-      <c r="D19" s="23">
-        <v>0</v>
-      </c>
-      <c r="E19" s="23"/>
-      <c r="F19" s="23">
-        <v>0</v>
-      </c>
-      <c r="G19" s="23"/>
+      <c r="D19" s="60">
+        <v>0</v>
+      </c>
+      <c r="E19" s="60"/>
+      <c r="F19" s="60">
+        <v>0</v>
+      </c>
+      <c r="G19" s="60"/>
       <c r="H19" s="6" t="s">
         <v>35</v>
       </c>
@@ -1986,19 +1989,19 @@
       </c>
     </row>
     <row r="20" spans="1:18" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="27" t="s">
+      <c r="A20" s="52" t="s">
         <v>25</v>
       </c>
-      <c r="B20" s="28"/>
+      <c r="B20" s="53"/>
       <c r="C20" s="13"/>
-      <c r="D20" s="24">
-        <v>0</v>
-      </c>
-      <c r="E20" s="24"/>
-      <c r="F20" s="24">
-        <v>0</v>
-      </c>
-      <c r="G20" s="24"/>
+      <c r="D20" s="39">
+        <v>0</v>
+      </c>
+      <c r="E20" s="39"/>
+      <c r="F20" s="39">
+        <v>0</v>
+      </c>
+      <c r="G20" s="39"/>
       <c r="H20" s="14">
         <v>1</v>
       </c>
@@ -2023,26 +2026,26 @@
     </row>
     <row r="21" spans="1:18" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="22" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="38" t="s">
+      <c r="A22" s="25" t="s">
         <v>65</v>
       </c>
-      <c r="B22" s="39"/>
-      <c r="C22" s="39"/>
-      <c r="D22" s="39"/>
-      <c r="E22" s="39"/>
-      <c r="F22" s="39"/>
-      <c r="G22" s="39"/>
-      <c r="H22" s="39"/>
-      <c r="I22" s="39"/>
-      <c r="J22" s="39"/>
-      <c r="K22" s="39"/>
-      <c r="L22" s="39"/>
-      <c r="M22" s="39"/>
-      <c r="N22" s="39"/>
-      <c r="O22" s="39"/>
-      <c r="P22" s="39"/>
-      <c r="Q22" s="39"/>
-      <c r="R22" s="40"/>
+      <c r="B22" s="26"/>
+      <c r="C22" s="26"/>
+      <c r="D22" s="26"/>
+      <c r="E22" s="26"/>
+      <c r="F22" s="26"/>
+      <c r="G22" s="26"/>
+      <c r="H22" s="26"/>
+      <c r="I22" s="26"/>
+      <c r="J22" s="26"/>
+      <c r="K22" s="26"/>
+      <c r="L22" s="26"/>
+      <c r="M22" s="26"/>
+      <c r="N22" s="26"/>
+      <c r="O22" s="26"/>
+      <c r="P22" s="26"/>
+      <c r="Q22" s="26"/>
+      <c r="R22" s="27"/>
     </row>
     <row r="23" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="9"/>
@@ -2058,7 +2061,7 @@
       <c r="E23" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="F23" s="59" t="s">
+      <c r="F23" s="23" t="s">
         <v>52</v>
       </c>
       <c r="G23" s="7" t="s">
@@ -2100,54 +2103,54 @@
     </row>
     <row r="24" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="9" t="s">
-        <v>91</v>
-      </c>
-      <c r="B24" s="22">
-        <v>0</v>
-      </c>
-      <c r="C24" s="22"/>
-      <c r="D24" s="22"/>
-      <c r="E24" s="22"/>
-      <c r="F24" s="22"/>
-      <c r="G24" s="22"/>
-      <c r="H24" s="22"/>
-      <c r="I24" s="22"/>
-      <c r="J24" s="22"/>
-      <c r="K24" s="22"/>
-      <c r="L24" s="22">
+        <v>90</v>
+      </c>
+      <c r="B24" s="43">
+        <v>0</v>
+      </c>
+      <c r="C24" s="43"/>
+      <c r="D24" s="43"/>
+      <c r="E24" s="43"/>
+      <c r="F24" s="43"/>
+      <c r="G24" s="43"/>
+      <c r="H24" s="43"/>
+      <c r="I24" s="43"/>
+      <c r="J24" s="43"/>
+      <c r="K24" s="43"/>
+      <c r="L24" s="43">
         <v>1</v>
       </c>
-      <c r="M24" s="22"/>
-      <c r="N24" s="22"/>
-      <c r="O24" s="22"/>
-      <c r="P24" s="22"/>
-      <c r="Q24" s="22"/>
-      <c r="R24" s="37"/>
+      <c r="M24" s="43"/>
+      <c r="N24" s="43"/>
+      <c r="O24" s="43"/>
+      <c r="P24" s="43"/>
+      <c r="Q24" s="43"/>
+      <c r="R24" s="47"/>
     </row>
     <row r="25" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="B25" s="22" t="s">
+      <c r="B25" s="43" t="s">
         <v>69</v>
       </c>
-      <c r="C25" s="22"/>
-      <c r="D25" s="22"/>
-      <c r="E25" s="22"/>
-      <c r="F25" s="22"/>
-      <c r="G25" s="22"/>
-      <c r="H25" s="22"/>
-      <c r="I25" s="22"/>
-      <c r="J25" s="22"/>
-      <c r="K25" s="22"/>
-      <c r="L25" s="22">
-        <v>0</v>
-      </c>
-      <c r="M25" s="22"/>
-      <c r="N25" s="22"/>
-      <c r="O25" s="22"/>
-      <c r="P25" s="22"/>
-      <c r="Q25" s="22"/>
+      <c r="C25" s="43"/>
+      <c r="D25" s="43"/>
+      <c r="E25" s="43"/>
+      <c r="F25" s="43"/>
+      <c r="G25" s="43"/>
+      <c r="H25" s="43"/>
+      <c r="I25" s="43"/>
+      <c r="J25" s="43"/>
+      <c r="K25" s="43"/>
+      <c r="L25" s="43">
+        <v>0</v>
+      </c>
+      <c r="M25" s="43"/>
+      <c r="N25" s="43"/>
+      <c r="O25" s="43"/>
+      <c r="P25" s="43"/>
+      <c r="Q25" s="43"/>
       <c r="R25" s="11">
         <v>1</v>
       </c>
@@ -2156,24 +2159,24 @@
       <c r="A26" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="B26" s="22" t="s">
+      <c r="B26" s="43" t="s">
         <v>68</v>
       </c>
-      <c r="C26" s="22"/>
-      <c r="D26" s="22"/>
-      <c r="E26" s="22"/>
-      <c r="F26" s="22"/>
-      <c r="G26" s="22"/>
-      <c r="H26" s="22"/>
-      <c r="I26" s="22"/>
-      <c r="J26" s="22"/>
-      <c r="K26" s="22"/>
-      <c r="L26" s="22"/>
-      <c r="M26" s="22"/>
-      <c r="N26" s="22"/>
-      <c r="O26" s="22"/>
-      <c r="P26" s="22"/>
-      <c r="Q26" s="22"/>
+      <c r="C26" s="43"/>
+      <c r="D26" s="43"/>
+      <c r="E26" s="43"/>
+      <c r="F26" s="43"/>
+      <c r="G26" s="43"/>
+      <c r="H26" s="43"/>
+      <c r="I26" s="43"/>
+      <c r="J26" s="43"/>
+      <c r="K26" s="43"/>
+      <c r="L26" s="43"/>
+      <c r="M26" s="43"/>
+      <c r="N26" s="43"/>
+      <c r="O26" s="43"/>
+      <c r="P26" s="43"/>
+      <c r="Q26" s="43"/>
       <c r="R26" s="11">
         <v>0</v>
       </c>
@@ -2194,8 +2197,8 @@
       <c r="E27" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="F27" s="60" t="s">
-        <v>92</v>
+      <c r="F27" s="24" t="s">
+        <v>91</v>
       </c>
       <c r="G27" s="6" t="s">
         <v>73</v>
@@ -2222,78 +2225,78 @@
         <v>82</v>
       </c>
       <c r="O27" s="6" t="s">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="P27" s="6" t="s">
         <v>82</v>
       </c>
       <c r="Q27" s="6" t="s">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="R27" s="12" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="28" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B28" s="6"/>
       <c r="C28" s="6"/>
       <c r="D28" s="6"/>
       <c r="E28" s="6" t="s">
-        <v>84</v>
-      </c>
-      <c r="F28" s="60"/>
+        <v>83</v>
+      </c>
+      <c r="F28" s="24"/>
       <c r="G28" s="6"/>
       <c r="H28" s="6"/>
       <c r="I28" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J28" s="6"/>
       <c r="K28" s="6"/>
       <c r="L28" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="M28" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="M28" s="6" t="s">
-        <v>85</v>
-      </c>
       <c r="N28" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="P28" s="6"/>
       <c r="Q28" s="6"/>
       <c r="R28" s="12" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="29" spans="1:18" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A29" s="19" t="s">
+        <v>86</v>
+      </c>
+      <c r="B29" s="39">
+        <v>0</v>
+      </c>
+      <c r="C29" s="39"/>
+      <c r="D29" s="39"/>
+      <c r="E29" s="39"/>
+      <c r="F29" s="39"/>
+      <c r="G29" s="39"/>
+      <c r="H29" s="39"/>
+      <c r="I29" s="39"/>
+      <c r="J29" s="39"/>
+      <c r="K29" s="39"/>
+      <c r="L29" s="40" t="s">
         <v>87</v>
       </c>
-      <c r="B29" s="24">
-        <v>0</v>
-      </c>
-      <c r="C29" s="24"/>
-      <c r="D29" s="24"/>
-      <c r="E29" s="24"/>
-      <c r="F29" s="24"/>
-      <c r="G29" s="24"/>
-      <c r="H29" s="24"/>
-      <c r="I29" s="24"/>
-      <c r="J29" s="24"/>
-      <c r="K29" s="24"/>
-      <c r="L29" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="M29" s="54"/>
-      <c r="N29" s="54"/>
-      <c r="O29" s="54"/>
-      <c r="P29" s="54"/>
-      <c r="Q29" s="55"/>
+      <c r="M29" s="41"/>
+      <c r="N29" s="41"/>
+      <c r="O29" s="41"/>
+      <c r="P29" s="41"/>
+      <c r="Q29" s="42"/>
       <c r="R29" s="15">
         <v>1</v>
       </c>
@@ -2301,31 +2304,31 @@
     <row r="30" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="31" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="32" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B32" s="58"/>
+      <c r="B32" s="22"/>
       <c r="F32"/>
     </row>
     <row r="33" spans="2:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B33" s="58"/>
+      <c r="B33" s="22"/>
       <c r="F33"/>
     </row>
     <row r="34" spans="2:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="58"/>
+      <c r="B34" s="22"/>
       <c r="F34"/>
     </row>
     <row r="35" spans="2:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="58"/>
+      <c r="B35" s="22"/>
       <c r="F35"/>
     </row>
     <row r="36" spans="2:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B36" s="58"/>
+      <c r="B36" s="22"/>
       <c r="F36"/>
     </row>
     <row r="37" spans="2:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B37" s="58"/>
+      <c r="B37" s="22"/>
       <c r="F37"/>
     </row>
     <row r="38" spans="2:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B38" s="58"/>
+      <c r="B38" s="22"/>
       <c r="F38"/>
     </row>
     <row r="39" spans="2:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -2340,42 +2343,25 @@
     <row r="48" spans="2:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="71">
-    <mergeCell ref="A10:N10"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="A6:T6"/>
-    <mergeCell ref="U6:Y6"/>
-    <mergeCell ref="Z6:AF6"/>
-    <mergeCell ref="A7:T7"/>
-    <mergeCell ref="U7:Y7"/>
-    <mergeCell ref="Z7:AF7"/>
-    <mergeCell ref="B29:K29"/>
-    <mergeCell ref="L29:Q29"/>
-    <mergeCell ref="B26:Q26"/>
-    <mergeCell ref="B25:K25"/>
-    <mergeCell ref="L25:Q25"/>
-    <mergeCell ref="Z2:AF2"/>
-    <mergeCell ref="A3:G3"/>
-    <mergeCell ref="H3:L3"/>
-    <mergeCell ref="M3:Q3"/>
-    <mergeCell ref="R3:T3"/>
-    <mergeCell ref="U3:Y3"/>
-    <mergeCell ref="Z3:AF3"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="H2:L2"/>
-    <mergeCell ref="M2:Q2"/>
-    <mergeCell ref="R2:T2"/>
-    <mergeCell ref="U2:Y2"/>
-    <mergeCell ref="Z4:AF4"/>
-    <mergeCell ref="A5:L5"/>
-    <mergeCell ref="M5:Q5"/>
-    <mergeCell ref="R5:T5"/>
-    <mergeCell ref="U5:Y5"/>
-    <mergeCell ref="Z5:AF5"/>
-    <mergeCell ref="A4:G4"/>
-    <mergeCell ref="H4:L4"/>
-    <mergeCell ref="M4:Q4"/>
-    <mergeCell ref="R4:T4"/>
-    <mergeCell ref="U4:Y4"/>
+    <mergeCell ref="D20:E20"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="F12:G12"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="F14:G14"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="F18:G18"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="F20:G20"/>
+    <mergeCell ref="D11:E11"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="D13:E13"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="D17:E17"/>
+    <mergeCell ref="F16:G16"/>
+    <mergeCell ref="D15:E16"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="D18:E18"/>
+    <mergeCell ref="D19:E19"/>
     <mergeCell ref="B24:K24"/>
     <mergeCell ref="L24:R24"/>
     <mergeCell ref="A22:R22"/>
@@ -2392,25 +2378,42 @@
     <mergeCell ref="A20:B20"/>
     <mergeCell ref="A16:B16"/>
     <mergeCell ref="F15:G15"/>
-    <mergeCell ref="F16:G16"/>
-    <mergeCell ref="D15:E16"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="D18:E18"/>
-    <mergeCell ref="D19:E19"/>
-    <mergeCell ref="D20:E20"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="F12:G12"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="F14:G14"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="F18:G18"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="F20:G20"/>
-    <mergeCell ref="D11:E11"/>
-    <mergeCell ref="D12:E12"/>
-    <mergeCell ref="D13:E13"/>
-    <mergeCell ref="D14:E14"/>
-    <mergeCell ref="D17:E17"/>
+    <mergeCell ref="Z4:AF4"/>
+    <mergeCell ref="A5:L5"/>
+    <mergeCell ref="M5:Q5"/>
+    <mergeCell ref="R5:T5"/>
+    <mergeCell ref="U5:Y5"/>
+    <mergeCell ref="Z5:AF5"/>
+    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="H4:L4"/>
+    <mergeCell ref="M4:Q4"/>
+    <mergeCell ref="R4:T4"/>
+    <mergeCell ref="U4:Y4"/>
+    <mergeCell ref="Z2:AF2"/>
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="H3:L3"/>
+    <mergeCell ref="M3:Q3"/>
+    <mergeCell ref="R3:T3"/>
+    <mergeCell ref="U3:Y3"/>
+    <mergeCell ref="Z3:AF3"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="H2:L2"/>
+    <mergeCell ref="M2:Q2"/>
+    <mergeCell ref="R2:T2"/>
+    <mergeCell ref="U2:Y2"/>
+    <mergeCell ref="B29:K29"/>
+    <mergeCell ref="L29:Q29"/>
+    <mergeCell ref="B26:Q26"/>
+    <mergeCell ref="B25:K25"/>
+    <mergeCell ref="L25:Q25"/>
+    <mergeCell ref="A10:N10"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="A6:T6"/>
+    <mergeCell ref="U6:Y6"/>
+    <mergeCell ref="Z6:AF6"/>
+    <mergeCell ref="A7:T7"/>
+    <mergeCell ref="U7:Y7"/>
+    <mergeCell ref="Z7:AF7"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
